--- a/storage/testing/payable-tax-no-project.xlsx
+++ b/storage/testing/payable-tax-no-project.xlsx
@@ -50,7 +50,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>AKN-1037</t>
+    <t>AKN-2032</t>
   </si>
   <si>
     <t>VENDOR</t>
